--- a/cc2652R7_DesignFiles/BOM/MCU075A-LP-CC2652R7 -RevA_BOM.xlsx
+++ b/cc2652R7_DesignFiles/BOM/MCU075A-LP-CC2652R7 -RevA_BOM.xlsx
@@ -1,24 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20378"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0488519\Desktop\TCF Updates\lp-cc2652r7\compliance\TCF Rev A\01-Bill of Materials\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2AFF9A-09E3-40C8-AF4A-F6386403CE42}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{55CBDF58-F61A-4596-BF45-B141942D7160}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -27,1628 +22,1648 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="537">
   <si>
-    <t>Capture CIS Standard Bill Of Materials - Standard Report</t>
-  </si>
-  <si>
-    <t>Report Created on Wednesday Aug 04 16:13:54 2021</t>
-  </si>
-  <si>
-    <t>Design Modify Date = Tuesday, August 03, 2021</t>
-  </si>
-  <si>
-    <t>RevCode = A</t>
-  </si>
-  <si>
-    <t>Title = LP-CC2652R7</t>
-  </si>
-  <si>
-    <t>Part Number</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Part Reference</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Vendor</t>
-  </si>
-  <si>
-    <t>Vendor Part Number</t>
-  </si>
-  <si>
-    <t>ROHS</t>
-  </si>
-  <si>
-    <t>REACH/SVHC Status</t>
-  </si>
-  <si>
-    <t>02-10342</t>
-  </si>
-  <si>
-    <t>C1 C9 C17 C18 C88 C89</t>
-  </si>
-  <si>
-    <t>12pF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC C0G/NP0, 12pF, 50V, -5%/+5%, -55DEGC/+125DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>MURATA</t>
-  </si>
-  <si>
-    <t>GCM1555C1H120JA16D</t>
-  </si>
-  <si>
-    <t>Compliant</t>
-  </si>
-  <si>
-    <t>Unaffected</t>
-  </si>
-  <si>
-    <t>02-10344</t>
-  </si>
-  <si>
-    <t>C2 C3 C4 C7 C50 C109 C166 C484</t>
-  </si>
-  <si>
-    <t>10nF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X7R, 10nF, 25V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GCM155R71E103KA37D</t>
-  </si>
-  <si>
-    <t>02-06085</t>
-  </si>
-  <si>
-    <t>C6 C78 C79 C80 C83 C84 C87</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X5R, 100nF, 10V, -10%/+10%, -55DEGC/+85DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>GRM033R61A104KE84D</t>
-  </si>
-  <si>
-    <t>02-07861</t>
-  </si>
-  <si>
-    <t>C8 C20 C30 C38 C39 C43 C46 C70 C71 C72 C73 C74 C75 C99 C101 C102 C104 C106 C107 C110 C114 C115 C116 C118 C119 C120 C125 C126 C127 C139 C140 C141 C152 C154 C158 C161 C162 C164 C175 C485</t>
-  </si>
-  <si>
-    <t>0.1uF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X7R, 0.1uF, 25V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GRM155R71E104KE14D</t>
-  </si>
-  <si>
-    <t>02-09025</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC C0G/NP0, 12pF, 50V, -5%/+5%, -55DEGC/+125DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>GRT0335C1H120JA02D</t>
-  </si>
-  <si>
-    <t>02-09024</t>
-  </si>
-  <si>
-    <t>C12 C21 C22</t>
-  </si>
-  <si>
-    <t>1pF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC C0G/NP0, 1pF, 50V, -0.25%/+0.25pF, -55DEGC/+125DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>GRT0335C1H1R0CA02D</t>
-  </si>
-  <si>
-    <t>02-09326</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>GRM0335C1H120JA01D</t>
-  </si>
-  <si>
-    <t>DNM</t>
-  </si>
-  <si>
-    <t>C15 C24</t>
-  </si>
-  <si>
-    <t>02-07863</t>
-  </si>
-  <si>
-    <t>C19 C40 C42 C44 C128 C133 C136 C137 C138 C145</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X5R, 1uF, 16V, -10%/+10%, -55DEGC/+85DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GRM155R61C105KA12D</t>
-  </si>
-  <si>
-    <t>02-06126</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>1.2pF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC C0G/NP0, 1.2pF, 50V, -0.1pF/+0.1pF, -55DEGC/+125DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>GRM0335C1H1R2BA01J</t>
-  </si>
-  <si>
-    <t>02-06058</t>
-  </si>
-  <si>
-    <t>C45 C48 C49 C143 C144 C149 C151 C155 C157 C159 C160 C163 C171</t>
-  </si>
-  <si>
-    <t>2.2uF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X5R, 2.2uF, 25V, -10%/+10%, -55DEGC/+85DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GRM155R61E225KE11D</t>
-  </si>
-  <si>
-    <t>02-10345</t>
-  </si>
-  <si>
-    <t>C47 C153 C172</t>
-  </si>
-  <si>
-    <t>15pF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC C0G/NP0, 15pF, 50V, -5%/+5%, -55DEGC/+125DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GRT1555C1H150JA02J</t>
-  </si>
-  <si>
-    <t>02-07629</t>
-  </si>
-  <si>
-    <t>C85 C86</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X5R, 4.7uF, 6.3V, -20%/+20%, -55DEGC/+85DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GRM155R60J475ME87D</t>
-  </si>
-  <si>
-    <t>02-07053</t>
-  </si>
-  <si>
-    <t>C103 C105 C113 C156 C165 C174</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC, X5R, 22uF, 6.3V, -20%/+20%, -55DEGC/+85DEGC, 0603, SMD</t>
-  </si>
-  <si>
-    <t>GRM188R60J226MEA0D</t>
-  </si>
-  <si>
-    <t>02-10346</t>
-  </si>
-  <si>
-    <t>C108</t>
-  </si>
-  <si>
-    <t>33nF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X7R, 33nF, 50V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GCM155R71H333KE02D</t>
-  </si>
-  <si>
-    <t>02-10341</t>
-  </si>
-  <si>
-    <t>C111</t>
-  </si>
-  <si>
-    <t>3.3uF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X5R, 3.3uF, 10V, -10%/+10%, -55DEGC/+85DEGC, 0603, SMD</t>
-  </si>
-  <si>
-    <t>SAMSUNG ELECTRO-MECHANICS</t>
-  </si>
-  <si>
-    <t>CL10A335KP8NNNC</t>
-  </si>
-  <si>
-    <t>C112</t>
-  </si>
-  <si>
-    <t>02-05775</t>
-  </si>
-  <si>
-    <t>C117 C121 C122 C142 C147 C168</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X7R, 10uF, 16V, -10%/+10%, -55DEGC/+125DEGC, 0805, SMD</t>
-  </si>
-  <si>
-    <t>CL21B106KOQNNNE</t>
-  </si>
-  <si>
-    <t>02-08708</t>
-  </si>
-  <si>
-    <t>C123 C135</t>
-  </si>
-  <si>
-    <t>270pF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC C0G/NP0, 270pF, 50V, -1%/+1%, -55DEGC/+125DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GRM1555C1H271FA01D</t>
-  </si>
-  <si>
-    <t>C124 C132 C134 C170</t>
-  </si>
-  <si>
-    <t>02-09156</t>
-  </si>
-  <si>
-    <t>C129</t>
-  </si>
-  <si>
-    <t>470pF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X7R, 470pF, 50V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GCM155R71H471KA37D</t>
-  </si>
-  <si>
-    <t>02-10347</t>
-  </si>
-  <si>
-    <t>C130</t>
-  </si>
-  <si>
-    <t>1nF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X7R, 1nF, 50V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GCM155R71H102KA37D</t>
-  </si>
-  <si>
-    <t>02-05294</t>
-  </si>
-  <si>
-    <t>C131</t>
-  </si>
-  <si>
-    <t>22nF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X7R, 22nF, 25V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>GRM155R71E223KA61D</t>
-  </si>
-  <si>
-    <t>02-07728</t>
-  </si>
-  <si>
-    <t>C146</t>
-  </si>
-  <si>
-    <t>47uF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X5R, 47uF, 10V, -20%/+20%, -55DEGC/+85DEGC, 0805, SMD</t>
-  </si>
-  <si>
-    <t>GRM21BR61A476ME15L</t>
-  </si>
-  <si>
-    <t>C169</t>
-  </si>
-  <si>
-    <t>02-08923</t>
-  </si>
-  <si>
-    <t>C486</t>
-  </si>
-  <si>
-    <t>220uF</t>
-  </si>
-  <si>
-    <t>CAPACITOR, CERAMIC X5R, 220uF, 6.3V, -20%/+20%, -55DEGC/+85DEGC, 1210, SMD</t>
-  </si>
-  <si>
-    <t>GRM32ER60J227ME05L</t>
-  </si>
-  <si>
-    <t>15-01287</t>
-  </si>
-  <si>
-    <t>CR1 CR5</t>
-  </si>
-  <si>
-    <t>GREEN LED</t>
-  </si>
-  <si>
-    <t>OPTO, LED, GREEN, 573nm, 2V, 0.02A, 0603, SMD</t>
-  </si>
-  <si>
-    <t>OSRAM</t>
-  </si>
-  <si>
-    <t>LG Q396-PS-35</t>
-  </si>
-  <si>
-    <t>15-01289</t>
-  </si>
-  <si>
-    <t>CR2 CR4</t>
-  </si>
-  <si>
-    <t>RED LED</t>
-  </si>
-  <si>
-    <t>OPTO, LED, RED, 633nm, 2V, 0.02A, 0603, SMD</t>
-  </si>
-  <si>
-    <t>LS Q976-NR-1</t>
-  </si>
-  <si>
-    <t>14-06172</t>
-  </si>
-  <si>
-    <t>CR6</t>
-  </si>
-  <si>
-    <t>TPD4E004DRY</t>
-  </si>
-  <si>
-    <t>DIODE, PROTECTION, ESD ARRAY, 4 CHANNEL, 6V TO 8V, -40DEGC/+85DEGC, SON6, SMD</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS</t>
-  </si>
-  <si>
-    <t>TPD4E004DRYR</t>
-  </si>
-  <si>
-    <t>14-05493</t>
-  </si>
-  <si>
-    <t>CR7 CR8</t>
-  </si>
-  <si>
-    <t>TPD6E004RSER</t>
-  </si>
-  <si>
-    <t>DIODE, PROTECTION, ESD ARRAY - 6 CHANNELS, 7V, -40DEGC/+85DEGC, QFN8, SMD</t>
-  </si>
-  <si>
-    <t>CR14</t>
-  </si>
-  <si>
-    <t>14-03076</t>
-  </si>
-  <si>
-    <t>CR15</t>
-  </si>
-  <si>
-    <t>MBR130T1</t>
-  </si>
-  <si>
-    <t>DIODE, SCHOTTKY, 1A, 30V, -65DEGC/+125DEGC, SOD-123, SMD</t>
-  </si>
-  <si>
-    <t>ON SEMICONDUCTOR</t>
-  </si>
-  <si>
-    <t>MBR130T1G</t>
-  </si>
-  <si>
-    <t>04-00470</t>
-  </si>
-  <si>
-    <t>FL1 FL2 FL4 FL5</t>
-  </si>
-  <si>
-    <t>BLM18HE152SN1</t>
-  </si>
-  <si>
-    <t>FILTER, EMI, FERRITE BEAD, 1500@100MHz, -25%/+25%, -55DEGC/+125DEGC, 0603, SMD</t>
-  </si>
-  <si>
-    <t>BLM18HE152SN1D</t>
-  </si>
-  <si>
-    <t>06-04997</t>
-  </si>
-  <si>
-    <t>J1 J2</t>
-  </si>
-  <si>
-    <t>SSQ-110-23-L-D</t>
-  </si>
-  <si>
-    <t>CONNECTOR, HEADER, FEMALE, STRAIGHT, 2 ROWS, 20 ROWS, 2.54mm, PTH</t>
-  </si>
-  <si>
-    <t>SAMTEC</t>
-  </si>
-  <si>
-    <t>06-04998</t>
-  </si>
-  <si>
-    <t>J6</t>
-  </si>
-  <si>
-    <t>105164-0001</t>
-  </si>
-  <si>
-    <t>CONNECTOR, USB, FEMALE, RIGHT ANGLE, 1 ROW, 5 PINS, PITCH 0.65mm, SMD</t>
-  </si>
-  <si>
-    <t>MOLEX</t>
-  </si>
-  <si>
-    <t>03-07266</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>6.8uH</t>
-  </si>
-  <si>
-    <t>INDUCTOR, STANDARD, CHIP, FERRITE CORE, SHIELDED, 6.8uH, -20%/+20%, 1.1A, -55DEGC/+125DEGC, 0805, SMD</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>MLZ2012N6R8LT000</t>
-  </si>
-  <si>
-    <t>03-07977</t>
-  </si>
-  <si>
-    <t>L12 L21</t>
-  </si>
-  <si>
-    <t>3.7nH</t>
-  </si>
-  <si>
-    <t>INDUCTOR, RF, CHIP, NON-MAGNETIC CORE, 3.7nH, -0.1nH/+0.1nH, 0.4A, -55DEGC/+125DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>LQP03TN3N7BZ2J</t>
-  </si>
-  <si>
-    <t>03-06937</t>
-  </si>
-  <si>
-    <t>L13 L14</t>
-  </si>
-  <si>
-    <t>3.4nH</t>
-  </si>
-  <si>
-    <t>INDUCTOR, RF, CHIP, NON-MAGNETIC CORE, 3.4nH, -0.1nH/+0.1nH, 0.45A, -55DEGC/+125DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>LQP03TN3N4B02J</t>
-  </si>
-  <si>
-    <t>04-00050</t>
-  </si>
-  <si>
-    <t>L332 L333 L334</t>
-  </si>
-  <si>
-    <t>BLM21PG221SN1</t>
-  </si>
-  <si>
-    <t>FILTER, EMI, FERRITE BEAD, 220@100MHz, -25%/+25%, -55DEGC/+125DEGC, 0805, SMD</t>
-  </si>
-  <si>
-    <t>BLM21PG221SN1D</t>
-  </si>
-  <si>
-    <t>19-00498</t>
-  </si>
-  <si>
-    <t>M1 M2 M3 M4 M5 M6 M7 M8 M9 M10 M14</t>
-  </si>
-  <si>
-    <t>SNT-100-BK-G</t>
-  </si>
-  <si>
-    <t>MECHANIC, SHUNT, CURRENT RATING 4.3A PER PIN, 2.54 X 5.08 X 6.1mm, BLACK</t>
-  </si>
-  <si>
-    <t>M11 M12 M13</t>
-  </si>
-  <si>
-    <t>06-05038</t>
-  </si>
-  <si>
-    <t>P1 P2 P10</t>
-  </si>
-  <si>
-    <t>BB02-HC031-KB1-603000</t>
-  </si>
-  <si>
-    <t>CONNECTOR, HEADER, MALE, STRAIGHT, 1 ROW, 3 PINS, PITCH 2.54mm, PTH</t>
-  </si>
-  <si>
-    <t>GRADCONN</t>
-  </si>
-  <si>
-    <t>06-05049</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>BB02-HJ221-KB1-603000</t>
-  </si>
-  <si>
-    <t>CONNECTOR, HEADER, MALE, STRAIGHT, 2 ROWS, 22 PINS, PITCH 2.54mm, PTH</t>
-  </si>
-  <si>
-    <t>06-00166</t>
-  </si>
-  <si>
-    <t>P5 P7</t>
-  </si>
-  <si>
-    <t>FTSH-105-01-F-DV-K</t>
-  </si>
-  <si>
-    <t>CONNECTOR, HEADER, MALE, STRAIGHT, 2 ROWS, 10 PINS, PITCH 1.27mm, SMD</t>
-  </si>
-  <si>
-    <t>06-04999</t>
-  </si>
-  <si>
-    <t>P6</t>
-  </si>
-  <si>
-    <t>BB02-HJ041-KB1-603000</t>
-  </si>
-  <si>
-    <t>CONNECTOR, HEADER, MALE, STRAIGHT, 2 ROWS, 4 PINS, PITCH 2.54mm, PTH</t>
-  </si>
-  <si>
-    <t>P8</t>
-  </si>
-  <si>
-    <t>06-02188</t>
-  </si>
-  <si>
-    <t>P11</t>
-  </si>
-  <si>
-    <t>SMA-10V21-TGG</t>
-  </si>
-  <si>
-    <t>CONNECTOR, COAX, RF, FEMALE, STRAIGHT, 1 PIN, SMD</t>
-  </si>
-  <si>
-    <t>HUS-TSAN</t>
-  </si>
-  <si>
-    <t>19-00925</t>
-  </si>
-  <si>
-    <t>PCB1</t>
-  </si>
-  <si>
-    <t>MCU075</t>
-  </si>
-  <si>
-    <t>NON COMPONENT, PCB, TEXAS INSTRUMENTS</t>
-  </si>
-  <si>
-    <t>PCB</t>
-  </si>
-  <si>
-    <t>01-22492</t>
-  </si>
-  <si>
-    <t>R1 R96 R97 R98 R105 R117 R118 R119 R136</t>
-  </si>
-  <si>
-    <t>100k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 100k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>VISHAY</t>
-  </si>
-  <si>
-    <t>CRCW0402100KJNED</t>
-  </si>
-  <si>
-    <t>Exempt</t>
-  </si>
-  <si>
-    <t>R2 R3</t>
-  </si>
-  <si>
-    <t>01-22487</t>
-  </si>
-  <si>
-    <t>R11</t>
-  </si>
-  <si>
-    <t>2.2k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 2.2k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04022K20JNED</t>
-  </si>
-  <si>
-    <t>01-22346</t>
-  </si>
-  <si>
-    <t>R14 R25</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 220, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW0402220RJNED</t>
-  </si>
-  <si>
-    <t>01-22345</t>
-  </si>
-  <si>
-    <t>R15 R23</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 180, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW0402180RJNED</t>
-  </si>
-  <si>
-    <t>01-22353</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>10k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 10k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040210K0JNED</t>
-  </si>
-  <si>
-    <t>01-22489</t>
-  </si>
-  <si>
-    <t>R18 R126 R353</t>
-  </si>
-  <si>
-    <t>4.7k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 4.7k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04024K70JNED</t>
-  </si>
-  <si>
-    <t>01-22482</t>
-  </si>
-  <si>
-    <t>R20 R55 R56 R57</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 100, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW0402100RJNED</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>01-22486</t>
-  </si>
-  <si>
-    <t>R27 R29 R30 R39</t>
-  </si>
-  <si>
-    <t>1k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 1k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04021K00JNED</t>
-  </si>
-  <si>
-    <t>01-22494</t>
-  </si>
-  <si>
-    <t>R28</t>
-  </si>
-  <si>
-    <t>4.87k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 4.87k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04024K87FKED</t>
-  </si>
-  <si>
-    <t>01-22481</t>
-  </si>
-  <si>
-    <t>R31</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 51, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040251R0JNED</t>
-  </si>
-  <si>
-    <t>01-22477</t>
-  </si>
-  <si>
-    <t>R32</t>
-  </si>
-  <si>
-    <t>33k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 33k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040233K0FKED</t>
-  </si>
-  <si>
-    <t>01-22491</t>
-  </si>
-  <si>
-    <t>R33 R132 R151</t>
-  </si>
-  <si>
-    <t>51k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 51k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040251K0JNED</t>
-  </si>
-  <si>
-    <t>01-22490</t>
-  </si>
-  <si>
-    <t>R34 R133 R135 R152</t>
-  </si>
-  <si>
-    <t>30k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 30k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040230K0JNED</t>
-  </si>
-  <si>
-    <t>R46 R47 R52</t>
-  </si>
-  <si>
-    <t>01-20043</t>
-  </si>
-  <si>
-    <t>R48 R49 R51 R89</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 0, 0R/+0.02R, 0.1W, 75V, -55DEGC/+155DEGC, 0603, SMD</t>
-  </si>
-  <si>
-    <t>CRCW06030000Z0EC</t>
-  </si>
-  <si>
-    <t>01-22488</t>
-  </si>
-  <si>
-    <t>R58</t>
-  </si>
-  <si>
-    <t>3.3k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 3.3k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04023K30JNED</t>
-  </si>
-  <si>
-    <t>R59 R60</t>
-  </si>
-  <si>
-    <t>01-22536</t>
-  </si>
-  <si>
-    <t>R61 R62 R63 R65 R114</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 100k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>TT ELECTRONICS</t>
-  </si>
-  <si>
-    <t>WCR0402-100KFA</t>
-  </si>
-  <si>
-    <t>01-04196</t>
-  </si>
-  <si>
-    <t>R82 R83 R92</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 10k, -5%/+5%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>CRCW020110K0JNED</t>
-  </si>
-  <si>
-    <t>01-04087</t>
-  </si>
-  <si>
-    <t>R84</t>
-  </si>
-  <si>
-    <t>12k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 12k, -1%/+1%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>CRCW020112K0FKED</t>
-  </si>
-  <si>
-    <t>01-22476</t>
-  </si>
-  <si>
-    <t>R87</t>
-  </si>
-  <si>
-    <t>1Meg</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 1M, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04021M00FKED</t>
-  </si>
-  <si>
-    <t>01-04172</t>
-  </si>
-  <si>
-    <t>R90 R91</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 1k, -5%/+5%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>CRCW02011K00JNED</t>
-  </si>
-  <si>
-    <t>01-04203</t>
-  </si>
-  <si>
-    <t>R93</t>
-  </si>
-  <si>
-    <t>20k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 20k, -5%/+5%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>CRCW020120K0JNED</t>
-  </si>
-  <si>
-    <t>01-01183</t>
-  </si>
-  <si>
-    <t>R94</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 22, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040222R0JNED</t>
-  </si>
-  <si>
-    <t>01-00128</t>
-  </si>
-  <si>
-    <t>R95 R101 R109 R120</t>
-  </si>
-  <si>
-    <t>1.2k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 1.2k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04021K20FKED</t>
-  </si>
-  <si>
-    <t>01-22495</t>
-  </si>
-  <si>
-    <t>R99 R100 R108 R131</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 0, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04020000Z0ED</t>
-  </si>
-  <si>
-    <t>01-00195</t>
-  </si>
-  <si>
-    <t>R102 R110</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 330, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW0402330RFKED</t>
-  </si>
-  <si>
-    <t>01-04307</t>
-  </si>
-  <si>
-    <t>R103 R112</t>
-  </si>
-  <si>
-    <t>4.99</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 4.99, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04024R99FKED</t>
-  </si>
-  <si>
-    <t>01-00234</t>
-  </si>
-  <si>
-    <t>R104 R113 R354</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 10, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040210R0FKED</t>
-  </si>
-  <si>
-    <t>R106 R111</t>
-  </si>
-  <si>
-    <t>01-03527</t>
-  </si>
-  <si>
-    <t>R107</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 1, -1%/+1%, 1W, 200V, -55DEGC/+155DEGC, 1218, SMD</t>
-  </si>
-  <si>
-    <t>CRCW12181R00FNEK</t>
-  </si>
-  <si>
-    <t>R115</t>
-  </si>
-  <si>
-    <t>01-04658</t>
-  </si>
-  <si>
-    <t>R116 R134</t>
-  </si>
-  <si>
-    <t>60.4k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 60.4k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040260K4FKED</t>
-  </si>
-  <si>
-    <t>01-01252</t>
-  </si>
-  <si>
-    <t>R121</t>
-  </si>
-  <si>
-    <t>22k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 22k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040222K0JNED</t>
-  </si>
-  <si>
-    <t>01-20687</t>
-  </si>
-  <si>
-    <t>R122</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 0.22, -1%/+1%, 0.125W, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>RCWE0402R220FKEA</t>
-  </si>
-  <si>
-    <t>01-06917</t>
-  </si>
-  <si>
-    <t>R123</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 82, -1%/+1%, 0.25W, 200V, -55DEGC/+155DEGC, 1206, SMD</t>
-  </si>
-  <si>
-    <t>CRCW120682R0FKEA</t>
-  </si>
-  <si>
-    <t>01-07315</t>
-  </si>
-  <si>
-    <t>R125</t>
-  </si>
-  <si>
-    <t>36.5</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 36.5, -1%/+1%, 0.5W, 200V, -55DEGC/+155DEGC, 1210, SMD</t>
-  </si>
-  <si>
-    <t>CRCW121036R5FKEA</t>
-  </si>
-  <si>
-    <t>01-01260</t>
-  </si>
-  <si>
-    <t>R127 R128 R129</t>
-  </si>
-  <si>
-    <t>47k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 47k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW040247K0JNED</t>
-  </si>
-  <si>
-    <t>01-00239</t>
-  </si>
-  <si>
-    <t>R130</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 2.2k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04022K20FKED</t>
-  </si>
-  <si>
-    <t>01-04542</t>
-  </si>
-  <si>
-    <t>R137</t>
-  </si>
-  <si>
-    <t>2.61k</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 2.61k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
-  </si>
-  <si>
-    <t>CRCW04022K61FKED</t>
-  </si>
-  <si>
-    <t>R138</t>
-  </si>
-  <si>
-    <t>01-04141</t>
-  </si>
-  <si>
-    <t>R140 R141 R142 R143 R144 R145 R146 R147 R148</t>
-  </si>
-  <si>
-    <t>RESISTOR, THICK FILM, 51, -5%/+5%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
-  </si>
-  <si>
-    <t>CRCW020151R0JNED</t>
-  </si>
-  <si>
-    <t>08-00293</t>
-  </si>
-  <si>
-    <t>SW1 SW2 SW3</t>
-  </si>
-  <si>
-    <t>1188E-1K2-V</t>
-  </si>
-  <si>
-    <t>SWITCH, TACT, 0.05A@250VAC, 0.05A@12VDC, 0.05A, 250V, SMD</t>
-  </si>
-  <si>
-    <t>DIPTRONICS</t>
-  </si>
-  <si>
-    <t>1188E-1K2-V-TR</t>
-  </si>
-  <si>
-    <t>18-36098</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>CC2652R74T0RGZR</t>
-  </si>
-  <si>
-    <t>IC, MICROCONTROLLER, TEXAS INSTRUMENTS, ARM CORTEX M4F, SIMPLELINK MULTIPROTOCOL 2.4GHZ WIRELESS MCU, 1.8V TO 3.8V, VQFN48-EP, SMD</t>
-  </si>
-  <si>
-    <t>18-31726</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>MX25R8035FZUIL0</t>
-  </si>
-  <si>
-    <t>IC, MEMORY, FLASH, SERIAL, 8Mbit, 1.65V TO 3.6V, USON8, SMD</t>
-  </si>
-  <si>
-    <t>MACRONIX</t>
-  </si>
-  <si>
-    <t>18-35458</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>MSP432E401YTPDT</t>
-  </si>
-  <si>
-    <t>IC, MICROCONTROLLER, SIMPLELINK ETHERNET MICROCONTROLLER, 2.97V TO 3.63V, TQFP128, SMD</t>
-  </si>
-  <si>
-    <t>18-29558</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>LM4040B25IDCK</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, PRECISION MICROPOWER SHUNT VOLTAGE REFERENCE, 2.5V, SC70-5, SMD</t>
-  </si>
-  <si>
-    <t>LM4040B25IDCKR</t>
-  </si>
-  <si>
-    <t>18-29530</t>
-  </si>
-  <si>
-    <t>U7 U42 U46</t>
-  </si>
-  <si>
-    <t>TPS79601DR</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, ULTRALOW-NOISE, HIGH PSRR, FAST, RF, 1A LOW-DROPOUT LINEAR REGULATORS, VIN:2.7V TO 5.5V, VOUT:1.2V TO 5.5V, SON8, SMD</t>
-  </si>
-  <si>
-    <t>TPS79601DRBR</t>
-  </si>
-  <si>
-    <t>18-29288</t>
-  </si>
-  <si>
-    <t>U8 U9 U10</t>
-  </si>
-  <si>
-    <t>SN74AVC4T245RSV</t>
-  </si>
-  <si>
-    <t>IC, DIGITAL, LOGIC, 4bit DUAL-SUPPLY BUS TRANSCEIVER 3 STATE OUTPUT, 1.2V TO 3.6V, UQFN16, SMD</t>
-  </si>
-  <si>
-    <t>SN74AVC4T245RSVR</t>
-  </si>
-  <si>
-    <t>18-26311</t>
-  </si>
-  <si>
-    <t>U15</t>
-  </si>
-  <si>
-    <t>USB3300-EZK</t>
-  </si>
-  <si>
-    <t>IC, DIGITAL, INTERFACE, HI-SPEED USB HOST, 3.3V, QFN32-EP, SMD</t>
-  </si>
-  <si>
-    <t>MICROCHIP</t>
-  </si>
-  <si>
-    <t>18-30805</t>
-  </si>
-  <si>
-    <t>U33 U38</t>
-  </si>
-  <si>
-    <t>TS3A24159DRC</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, 0.3R DUAL SPDT ANALOG SWITCH DUAL-CHANNEL 2:1 MULTIPLEXER/DEMULTIPLEXER, 1.65V TO 3.6V, SON10-EP, SMD</t>
-  </si>
-  <si>
-    <t>TS3A24159DRCR</t>
-  </si>
-  <si>
-    <t>18-27150</t>
-  </si>
-  <si>
-    <t>U34</t>
-  </si>
-  <si>
-    <t>SN74LVC2G74DCU</t>
-  </si>
-  <si>
-    <t>IC, DIGITAL, LOGIC, D-TYPE FLIP-FLOP WITH CLEAR AND PRESET, 1.65V TO 5.5V, VSSOP8, SMD</t>
-  </si>
-  <si>
-    <t>SN74LVC2G74DCUR</t>
-  </si>
-  <si>
-    <t>18-33431</t>
-  </si>
-  <si>
-    <t>U35</t>
-  </si>
-  <si>
-    <t>ADS127L01IPBS</t>
-  </si>
-  <si>
-    <t>IC, MIXED, 24-BIT WIDE-BANDWIDTH ANALOG TO DIGITAL CONVERTER, 2.7V TO 3.6V/1.7V TO 3.6V, TQFP32, SMD</t>
-  </si>
-  <si>
-    <t>18-34413</t>
-  </si>
-  <si>
-    <t>U36</t>
-  </si>
-  <si>
-    <t>INA118UB</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, INSTRUMENTATION AMPLIFIER, -/+15V, SO8, SMD</t>
-  </si>
-  <si>
-    <t>18-34391</t>
-  </si>
-  <si>
-    <t>U37</t>
-  </si>
-  <si>
-    <t>THS4551IRUN</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, LOW NOISE, PRECISION, 150MHz, FULLY DIFFERENTIAL AMPLIFIER, 2.7V TO 5.4V, QFN10-EP, SMD</t>
-  </si>
-  <si>
-    <t>THS4551IRUNR</t>
-  </si>
-  <si>
-    <t>18-30809</t>
-  </si>
-  <si>
-    <t>U39</t>
-  </si>
-  <si>
-    <t>TS3A4751RUCR</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, 0.9R LOW-VOLTAGE SINGLE-SUPPLY QUAD SPST ANALOG SWITCH, 1.6V TO 3.6V, QFN14, SMD</t>
-  </si>
-  <si>
-    <t>18-34390</t>
-  </si>
-  <si>
-    <t>U40</t>
-  </si>
-  <si>
-    <t>REF6025IDGK</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, HIGH PRECISION VOLTAGE REFERENCE, VIN:3V TO 5.5V, VOUT:2.5V, VSSOP8, SMD</t>
-  </si>
-  <si>
-    <t>REF6025IDGKR</t>
-  </si>
-  <si>
-    <t>18-32984</t>
-  </si>
-  <si>
-    <t>U41</t>
-  </si>
-  <si>
-    <t>OPA320AIDBV</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, RAIL-TO-RAIL I/O CMOS OPERATIONAL AMPLIFIER, -/+0.9V TO 5.5V, SOT23-5, SMD</t>
-  </si>
-  <si>
-    <t>OPA320AIDBVT</t>
-  </si>
-  <si>
-    <t>18-32950</t>
-  </si>
-  <si>
-    <t>U43</t>
-  </si>
-  <si>
-    <t>LP5907MFX-1.8</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, 0.25A LINEAR REGULATOR FOR RF AND ANALOG CIRCUITS-REQUIRES NO BYPASS CAPACITOR, VIN:2.2V TO 5.5V, VOUT: 1.8V, SOT23-5, SMD</t>
-  </si>
-  <si>
-    <t>LP5907MFX-1.8/NOPB</t>
-  </si>
-  <si>
-    <t>18-33642</t>
-  </si>
-  <si>
-    <t>U44</t>
-  </si>
-  <si>
-    <t>TPS73101DBV</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, 0.15A LOW DROPOUT REGULATOR WITH REVERSE CURRENT PROTECTION, VIN:1.7V TO 5.5V, VOUT:1.2V TO 5.5V, SOT23-5, SMD</t>
-  </si>
-  <si>
-    <t>TPS73101DBVR</t>
-  </si>
-  <si>
-    <t>U45</t>
-  </si>
-  <si>
-    <t>18-34886</t>
-  </si>
-  <si>
-    <t>U47</t>
-  </si>
-  <si>
-    <t>TPS259530DSG</t>
-  </si>
-  <si>
-    <t>IC, ANALOG, EFUSE WITH FAST OVERVOLTAGE PROTECTION, 2.7V TO 18V, WSON8-EP, SMD</t>
-  </si>
-  <si>
-    <t>TPS259530DSGR</t>
-  </si>
-  <si>
-    <t>12-01495</t>
-  </si>
-  <si>
-    <t>Y1</t>
-  </si>
-  <si>
-    <t>32.768kHz</t>
-  </si>
-  <si>
-    <t>CRYSTAL, RESONATOR, 32.768kHz, -40DEGC/+125DEGC, SMD</t>
-  </si>
-  <si>
-    <t>TAI-SAW</t>
-  </si>
-  <si>
-    <t>TZ1166C</t>
-  </si>
-  <si>
-    <t>12-01494</t>
-  </si>
-  <si>
-    <t>Y2</t>
-  </si>
-  <si>
-    <t>48MHz</t>
-  </si>
-  <si>
-    <t>CRYSTAL, RESONATOR, 48MHz, -16PPM/+16PPM, -40DEGC/+105DEGC, SMD</t>
-  </si>
-  <si>
-    <t>TZ2365C</t>
-  </si>
-  <si>
-    <t>12-00745</t>
-  </si>
-  <si>
-    <t>Y3</t>
-  </si>
-  <si>
-    <t>16MHz</t>
-  </si>
-  <si>
-    <t>CRYSTAL, RESONATOR, 16MHz, -30PPM/+30PPM, -40DEGC/+85DEGC, SMD</t>
-  </si>
-  <si>
-    <t>NIHON DEMPA KOGYO</t>
-  </si>
-  <si>
-    <t>NX3225GA-16.000M-STD-CRG-1</t>
-  </si>
-  <si>
-    <t>12-00730</t>
-  </si>
-  <si>
-    <t>Y4</t>
-  </si>
-  <si>
-    <t>24MHz</t>
-  </si>
-  <si>
-    <t>CRYSTAL, RESONATOR, 24MHz, -50PPM/+50PPM, -40DEGC/+85DEGC, SMD</t>
-  </si>
-  <si>
-    <t>EPSON</t>
-  </si>
-  <si>
-    <t>FA-238 24.0000MB50X-W0</t>
-  </si>
-  <si>
-    <t>12-01320</t>
-  </si>
-  <si>
-    <t>Y5</t>
-  </si>
-  <si>
-    <t>16.384MHz</t>
-  </si>
-  <si>
-    <t>CRYSTAL, OSCILLATOR, XO, 16.384MHz, -50PPM/+50PPM, 3.3V, -20DEGC/+70DEGC, SMD</t>
-  </si>
-  <si>
-    <t>CTS COMPONENTS</t>
-  </si>
-  <si>
-    <t>636L3C016M38400</t>
+    <t xml:space="preserve">Capture CIS Standard Bill Of Materials - Standard Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report Created on Wednesday Aug 04 16:13:54 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design Modify Date = Tuesday, August 03, 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RevCode = A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title = LP-CC2652R7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor Part Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REACH/SVHC Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-10342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 C9 C17 C18 C88 C89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC C0G/NP0, 12pF, 50V, -5%/+5%, -55DEGC/+125DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MURATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCM1555C1H120JA16D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unaffected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-10344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 C3 C4 C7 C50 C109 C166 C484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X7R, 10nF, 25V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCM155R71E103KA37D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-06085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6 C78 C79 C80 C83 C84 C87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X5R, 100nF, 10V, -10%/+10%, -55DEGC/+85DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM033R61A104KE84D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-07861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8 C20 C30 C38 C39 C43 C46 C70 C71 C72 C73 C74 C75 C99 C101 C102 C104 C106 C107 C110 C114 C115 C116 C118 C119 C120 C125 C126 C127 C139 C140 C141 C152 C154 C158 C161 C162 C164 C175 C485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X7R, 0.1uF, 25V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM155R71E104KE14D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-09025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC C0G/NP0, 12pF, 50V, -5%/+5%, -55DEGC/+125DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRT0335C1H120JA02D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-09024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C12 C21 C22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC C0G/NP0, 1pF, 50V, -0.25%/+0.25pF, -55DEGC/+125DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRT0335C1H1R0CA02D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-09326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM0335C1H120JA01D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15 C24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-07863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19 C40 C42 C44 C128 C133 C136 C137 C138 C145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X5R, 1uF, 16V, -10%/+10%, -55DEGC/+85DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM155R61C105KA12D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-06126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC C0G/NP0, 1.2pF, 50V, -0.1pF/+0.1pF, -55DEGC/+125DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM0335C1H1R2BA01J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-06058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C45 C48 C49 C143 C144 C149 C151 C155 C157 C159 C160 C163 C171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X5R, 2.2uF, 25V, -10%/+10%, -55DEGC/+85DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM155R61E225KE11D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-10345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C47 C153 C172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC C0G/NP0, 15pF, 50V, -5%/+5%, -55DEGC/+125DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRT1555C1H150JA02J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-07629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C85 C86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X5R, 4.7uF, 6.3V, -20%/+20%, -55DEGC/+85DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM155R60J475ME87D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-07053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C103 C105 C113 C156 C165 C174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC, X5R, 22uF, 6.3V, -20%/+20%, -55DEGC/+85DEGC, 0603, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM188R60J226MEA0D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-10346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X7R, 33nF, 50V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCM155R71H333KE02D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-10341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X5R, 3.3uF, 10V, -10%/+10%, -55DEGC/+85DEGC, 0603, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMSUNG ELECTRO-MECHANICS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL10A335KP8NNNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-05775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C117 C121 C122 C142 C147 C168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X7R, 10uF, 16V, -10%/+10%, -55DEGC/+125DEGC, 0805, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL21B106KOQNNNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-08708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C123 C135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC C0G/NP0, 270pF, 50V, -1%/+1%, -55DEGC/+125DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM1555C1H271FA01D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C124 C132 C134 C170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-09156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X7R, 470pF, 50V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCM155R71H471KA37D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-10347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X7R, 1nF, 50V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCM155R71H102KA37D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-05294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X7R, 22nF, 25V, -10%/+10%, -55DEGC/+125DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM155R71E223KA61D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-07728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X5R, 47uF, 10V, -20%/+20%, -55DEGC/+85DEGC, 0805, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM21BR61A476ME15L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-08923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITOR, CERAMIC X5R, 220uF, 6.3V, -20%/+20%, -55DEGC/+85DEGC, 1210, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM32ER60J227ME05L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-01287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR1 CR5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREEN LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTO, LED, GREEN, 573nm, 2V, 0.02A, 0603, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSRAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LG Q396-PS-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-01289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR2 CR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTO, LED, RED, 633nm, 2V, 0.02A, 0603, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LS Q976-NR-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-06172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPD4E004DRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIODE, PROTECTION, ESD ARRAY, 4 CHANNEL, 6V TO 8V, -40DEGC/+85DEGC, SON6, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEXAS INSTRUMENTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPD4E004DRYR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-05493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR7 CR8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPD6E004RSER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIODE, PROTECTION, ESD ARRAY - 6 CHANNELS, 7V, -40DEGC/+85DEGC, QFN8, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-03076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBR130T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIODE, SCHOTTKY, 1A, 30V, -65DEGC/+125DEGC, SOD-123, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON SEMICONDUCTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBR130T1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04-00470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FL1 FL2 FL4 FL5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLM18HE152SN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTER, EMI, FERRITE BEAD, 1500@100MHz, -25%/+25%, -55DEGC/+125DEGC, 0603, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLM18HE152SN1D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06-04997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J1 J2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSQ-110-23-L-D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONNECTOR, HEADER, FEMALE, STRAIGHT, 2 ROWS, 20 ROWS, 2.54mm, PTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMTEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06-04998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105164-0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONNECTOR, USB, FEMALE, RIGHT ANGLE, 1 ROW, 5 PINS, PITCH 0.65mm, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOLEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03-07266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8uH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDUCTOR, STANDARD, CHIP, FERRITE CORE, SHIELDED, 6.8uH, -20%/+20%, 1.1A, -55DEGC/+125DEGC, 0805, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TDK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLZ2012N6R8LT000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03-07977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L12 L21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDUCTOR, RF, CHIP, NON-MAGNETIC CORE, 3.7nH, -0.1nH/+0.1nH, 0.4A, -55DEGC/+125DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LQP03TN3N7BZ2J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03-06937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L13 L14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDUCTOR, RF, CHIP, NON-MAGNETIC CORE, 3.4nH, -0.1nH/+0.1nH, 0.45A, -55DEGC/+125DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LQP03TN3N4B02J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04-00050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L332 L333 L334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLM21PG221SN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTER, EMI, FERRITE BEAD, 220@100MHz, -25%/+25%, -55DEGC/+125DEGC, 0805, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLM21PG221SN1D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19-00498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 M2 M3 M4 M5 M6 M7 M8 M9 M10 M14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNT-100-BK-G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHANIC, SHUNT, CURRENT RATING 4.3A PER PIN, 2.54 X 5.08 X 6.1mm, BLACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M11 M12 M13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06-05038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 P2 P10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BB02-HC031-KB1-603000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONNECTOR, HEADER, MALE, STRAIGHT, 1 ROW, 3 PINS, PITCH 2.54mm, PTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRADCONN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06-05049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BB02-HJ221-KB1-603000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONNECTOR, HEADER, MALE, STRAIGHT, 2 ROWS, 22 PINS, PITCH 2.54mm, PTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06-00166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5 P7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTSH-105-01-F-DV-K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONNECTOR, HEADER, MALE, STRAIGHT, 2 ROWS, 10 PINS, PITCH 1.27mm, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06-04999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BB02-HJ041-KB1-603000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONNECTOR, HEADER, MALE, STRAIGHT, 2 ROWS, 4 PINS, PITCH 2.54mm, PTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06-02188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA-10V21-TGG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONNECTOR, COAX, RF, FEMALE, STRAIGHT, 1 PIN, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUS-TSAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19-00925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCU075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NON COMPONENT, PCB, TEXAS INSTRUMENTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1 R96 R97 R98 R105 R117 R118 R119 R136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 100k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VISHAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW0402100KJNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2 R3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 2.2k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04022K20JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R14 R25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 220, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW0402220RJNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R15 R23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 180, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW0402180RJNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 10k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040210K0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R18 R126 R353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 4.7k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04024K70JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R20 R55 R56 R57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 100, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW0402100RJNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R27 R29 R30 R39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 1k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04021K00JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 4.87k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04024K87FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 51, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040251R0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 33k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040233K0FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R33 R132 R151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 51k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040251K0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R34 R133 R135 R152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 30k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040230K0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R46 R47 R52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-20043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R48 R49 R51 R89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 0, 0R/+0.02R, 0.1W, 75V, -55DEGC/+155DEGC, 0603, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW06030000Z0EC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 3.3k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04023K30JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R59 R60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R61 R62 R63 R65 R114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 100k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TT ELECTRONICS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WCR0402-100KFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-04196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R82 R83 R92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 10k, -5%/+5%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW020110K0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-04087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 12k, -1%/+1%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW020112K0FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1Meg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 1M, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04021M00FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-04172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R90 R91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 1k, -5%/+5%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW02011K00JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-04203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 20k, -5%/+5%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW020120K0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-01183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 22, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040222R0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-00128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R95 R101 R109 R120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 1.2k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04021K20FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-22495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R99 R100 R108 R131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 0, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04020000Z0ED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-00195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R102 R110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 330, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW0402330RFKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-04307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R103 R112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 4.99, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04024R99FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-00234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R104 R113 R354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 10, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040210R0FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R106 R111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-03527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 1, -1%/+1%, 1W, 200V, -55DEGC/+155DEGC, 1218, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW12181R00FNEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-04658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R116 R134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 60.4k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040260K4FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-01252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 22k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040222K0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-20687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 0.22, -1%/+1%, 0.125W, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCWE0402R220FKEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-06917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 82, -1%/+1%, 0.25W, 200V, -55DEGC/+155DEGC, 1206, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW120682R0FKEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-07315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 36.5, -1%/+1%, 0.5W, 200V, -55DEGC/+155DEGC, 1210, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW121036R5FKEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-01260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R127 R128 R129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 47k, -5%/+5%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW040247K0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-00239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 2.2k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04022K20FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-04542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 2.61k, -1%/+1%, 0.063W, 50V, -55DEGC/+155DEGC, 0402, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW04022K61FKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-04141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R140 R141 R142 R143 R144 R145 R146 R147 R148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTOR, THICK FILM, 51, -5%/+5%, 0.05W, 30V, -55DEGC/+155DEGC, 0201, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW020151R0JNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08-00293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW1 SW2 SW3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1188E-1K2-V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWITCH, TACT, 0.05A@250VAC, 0.05A@12VDC, 0.05A, 250V, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIPTRONICS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1188E-1K2-V-TR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-36098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC2652R74T0RGZR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, MICROCONTROLLER, TEXAS INSTRUMENTS, ARM CORTEX M4F, SIMPLELINK MULTIPROTOCOL 2.4GHZ WIRELESS MCU, 1.8V TO 3.8V, VQFN48-EP, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-31726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MX25R8035FZUIL0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, MEMORY, FLASH, SERIAL, 8Mbit, 1.65V TO 3.6V, USON8, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACRONIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-35458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSP432E401YTPDT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, MICROCONTROLLER, SIMPLELINK ETHERNET MICROCONTROLLER, 2.97V TO 3.63V, TQFP128, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-29558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LM4040B25IDCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, PRECISION MICROPOWER SHUNT VOLTAGE REFERENCE, 2.5V, SC70-5, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LM4040B25IDCKR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-29530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U7 U42 U46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPS79601DR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, ULTRALOW-NOISE, HIGH PSRR, FAST, RF, 1A LOW-DROPOUT LINEAR REGULATORS, VIN:2.7V TO 5.5V, VOUT:1.2V TO 5.5V, SON8, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPS79601DRBR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-29288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U8 U9 U10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SN74AVC4T245RSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, DIGITAL, LOGIC, 4bit DUAL-SUPPLY BUS TRANSCEIVER 3 STATE OUTPUT, 1.2V TO 3.6V, UQFN16, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SN74AVC4T245RSVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-26311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB3300-EZK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, DIGITAL, INTERFACE, HI-SPEED USB HOST, 3.3V, QFN32-EP, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICROCHIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-30805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U33 U38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS3A24159DRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, 0.3R DUAL SPDT ANALOG SWITCH DUAL-CHANNEL 2:1 MULTIPLEXER/DEMULTIPLEXER, 1.65V TO 3.6V, SON10-EP, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS3A24159DRCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-27150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SN74LVC2G74DCU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, DIGITAL, LOGIC, D-TYPE FLIP-FLOP WITH CLEAR AND PRESET, 1.65V TO 5.5V, VSSOP8, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SN74LVC2G74DCUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-33431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADS127L01IPBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, MIXED, 24-BIT WIDE-BANDWIDTH ANALOG TO DIGITAL CONVERTER, 2.7V TO 3.6V/1.7V TO 3.6V, TQFP32, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-34413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INA118UB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, INSTRUMENTATION AMPLIFIER, -/+15V, SO8, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-34391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THS4551IRUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, LOW NOISE, PRECISION, 150MHz, FULLY DIFFERENTIAL AMPLIFIER, 2.7V TO 5.4V, QFN10-EP, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THS4551IRUNR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-30809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS3A4751RUCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, 0.9R LOW-VOLTAGE SINGLE-SUPPLY QUAD SPST ANALOG SWITCH, 1.6V TO 3.6V, QFN14, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-34390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF6025IDGK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, HIGH PRECISION VOLTAGE REFERENCE, VIN:3V TO 5.5V, VOUT:2.5V, VSSOP8, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF6025IDGKR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-32984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPA320AIDBV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, RAIL-TO-RAIL I/O CMOS OPERATIONAL AMPLIFIER, -/+0.9V TO 5.5V, SOT23-5, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPA320AIDBVT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-32950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP5907MFX-1.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, 0.25A LINEAR REGULATOR FOR RF AND ANALOG CIRCUITS-REQUIRES NO BYPASS CAPACITOR, VIN:2.2V TO 5.5V, VOUT: 1.8V, SOT23-5, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP5907MFX-1.8/NOPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-33642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPS73101DBV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, 0.15A LOW DROPOUT REGULATOR WITH REVERSE CURRENT PROTECTION, VIN:1.7V TO 5.5V, VOUT:1.2V TO 5.5V, SOT23-5, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPS73101DBVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-34886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPS259530DSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC, ANALOG, EFUSE WITH FAST OVERVOLTAGE PROTECTION, 2.7V TO 18V, WSON8-EP, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPS259530DSGR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-01495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.768kHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYSTAL, RESONATOR, 32.768kHz, -40DEGC/+125DEGC, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAI-SAW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZ1166C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-01494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48MHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYSTAL, RESONATOR, 48MHz, -16PPM/+16PPM, -40DEGC/+105DEGC, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZ2365C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-00745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16MHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYSTAL, RESONATOR, 16MHz, -30PPM/+30PPM, -40DEGC/+85DEGC, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIHON DEMPA KOGYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NX3225GA-16.000M-STD-CRG-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-00730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24MHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYSTAL, RESONATOR, 24MHz, -50PPM/+50PPM, -40DEGC/+85DEGC, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FA-238 24.0000MB50X-W0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-01320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.384MHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYSTAL, OSCILLATOR, XO, 16.384MHz, -50PPM/+50PPM, 3.3V, -20DEGC/+70DEGC, SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTS COMPONENTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">636L3C016M38400</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="@"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1660,7 +1675,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -1668,334 +1683,71 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4472C4"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C0CEAC0-CA36-46E9-B948-255C01FEF896}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I124"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2005,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2016,22 +1768,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2060,11 +1812,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2089,11 +1841,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -2118,11 +1870,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -2147,11 +1899,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="1" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -2176,11 +1928,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -2205,11 +1957,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -2234,11 +1986,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2263,11 +2015,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2292,11 +2044,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -2321,11 +2073,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -2350,11 +2102,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -2379,11 +2131,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -2408,11 +2160,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2437,11 +2189,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2466,11 +2218,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -2495,11 +2247,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2524,11 +2276,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2553,11 +2305,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2582,11 +2334,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2611,11 +2363,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2640,11 +2392,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2669,11 +2421,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2698,11 +2450,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2727,11 +2479,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2756,11 +2508,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2785,11 +2537,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2814,11 +2566,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2843,11 +2595,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -2872,11 +2624,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2901,11 +2653,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -2930,11 +2682,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2959,11 +2711,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2988,11 +2740,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -3017,11 +2769,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -3046,11 +2798,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -3075,11 +2827,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -3104,11 +2856,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -3133,11 +2885,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -3162,11 +2914,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -3191,11 +2943,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -3220,11 +2972,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -3249,11 +3001,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -3278,11 +3030,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -3307,11 +3059,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -3336,11 +3088,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -3365,11 +3117,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -3394,11 +3146,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -3423,11 +3175,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -3452,11 +3204,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -3481,11 +3233,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -3510,11 +3262,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -3539,11 +3291,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -3568,11 +3320,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -3597,11 +3349,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C61" s="2" t="s">
@@ -3626,11 +3378,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -3655,11 +3407,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C63" s="2" t="s">
@@ -3684,11 +3436,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -3713,11 +3465,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -3742,11 +3494,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -3771,11 +3523,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -3800,11 +3552,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -3829,11 +3581,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -3858,11 +3610,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C70" s="2" t="s">
@@ -3887,11 +3639,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -3916,11 +3668,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C72" s="2" t="s">
@@ -3945,11 +3697,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C73" s="2" t="s">
@@ -3974,11 +3726,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -4003,11 +3755,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
@@ -4032,11 +3784,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -4061,11 +3813,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C77" s="2" t="s">
@@ -4090,11 +3842,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C78" s="2" t="s">
@@ -4119,11 +3871,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C79" s="2" t="s">
@@ -4148,11 +3900,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C80" s="2" t="s">
@@ -4177,11 +3929,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C81" s="2" t="s">
@@ -4206,11 +3958,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C82" s="2" t="s">
@@ -4235,11 +3987,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C83" s="2" t="s">
@@ -4264,11 +4016,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C84" s="2" t="s">
@@ -4293,11 +4045,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C85" s="2" t="s">
@@ -4322,11 +4074,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C86" s="2" t="s">
@@ -4351,11 +4103,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="s">
@@ -4380,11 +4132,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C88" s="2" t="s">
@@ -4409,11 +4161,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="s">
@@ -4438,11 +4190,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C90" s="2" t="s">
@@ -4467,11 +4219,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C91" s="2" t="s">
@@ -4496,11 +4248,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C92" s="2" t="s">
@@ -4525,11 +4277,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C93" s="2" t="s">
@@ -4554,11 +4306,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C94" s="2" t="s">
@@ -4583,11 +4335,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
@@ -4612,11 +4364,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C96" s="2" t="s">
@@ -4641,11 +4393,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C97" s="2" t="s">
@@ -4670,11 +4422,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="s">
@@ -4699,11 +4451,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C99" s="2" t="s">
@@ -4728,11 +4480,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C100" s="2" t="s">
@@ -4757,11 +4509,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C101" s="2" t="s">
@@ -4786,11 +4538,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B102" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C102" s="2" t="s">
@@ -4815,11 +4567,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B103" s="1">
+      <c r="B103" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C103" s="2" t="s">
@@ -4844,11 +4596,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B104" s="1">
+      <c r="B104" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C104" s="2" t="s">
@@ -4873,11 +4625,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B105" s="1">
+      <c r="B105" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C105" s="2" t="s">
@@ -4902,11 +4654,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="B106" s="1">
+      <c r="B106" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C106" s="2" t="s">
@@ -4931,11 +4683,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B107" s="1">
+      <c r="B107" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C107" s="2" t="s">
@@ -4960,11 +4712,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C108" s="2" t="s">
@@ -4989,11 +4741,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B109" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C109" s="2" t="s">
@@ -5018,11 +4770,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C110" s="2" t="s">
@@ -5047,11 +4799,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B111" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C111" s="2" t="s">
@@ -5076,11 +4828,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C112" s="2" t="s">
@@ -5105,11 +4857,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C113" s="2" t="s">
@@ -5134,11 +4886,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C114" s="2" t="s">
@@ -5163,11 +4915,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C115" s="2" t="s">
@@ -5192,11 +4944,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C116" s="2" t="s">
@@ -5221,11 +4973,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C117" s="2" t="s">
@@ -5250,11 +5002,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B118" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="s">
@@ -5279,11 +5031,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B119" s="1">
+      <c r="B119" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C119" s="2" t="s">
@@ -5308,11 +5060,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B120" s="1">
+      <c r="B120" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -5337,11 +5089,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B121" s="1">
+      <c r="B121" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C121" s="2" t="s">
@@ -5366,11 +5118,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="B122" s="1">
+      <c r="B122" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C122" s="2" t="s">
@@ -5395,11 +5147,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="B123" s="1">
+      <c r="B123" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C123" s="2" t="s">
@@ -5424,11 +5176,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="B124" s="1">
+      <c r="B124" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C124" s="2" t="s">
@@ -5454,6 +5206,12 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>